--- a/data/hinghua_rhymes.xlsx
+++ b/data/hinghua_rhymes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hinghua-singging\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\hinghua-singging\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCA5DAD-1B46-4E0C-9236-B8D4BD235A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D420CC-16B6-449E-BE74-1F83D5162738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{C75A4579-A8D3-4C66-A68D-C01FA9D4FF86}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12100" windowHeight="15370" xr2:uid="{C75A4579-A8D3-4C66-A68D-C01FA9D4FF86}"/>
   </bookViews>
   <sheets>
     <sheet name="hinghua_rhymes" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="315">
   <si>
     <t>平話字</t>
   </si>
@@ -158,20 +158,6 @@
     <t>e̤</t>
   </si>
   <si>
-    <r>
-      <t>所初助</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>螺腡坐戴推改脆</t>
-    </r>
-  </si>
-  <si>
     <t>[*ø]</t>
   </si>
   <si>
@@ -191,9 +177,6 @@
     </r>
   </si>
   <si>
-    <t>斷卵鑽酸全頓褪</t>
-  </si>
-  <si>
     <t>[*ø̃]</t>
   </si>
   <si>
@@ -225,20 +208,6 @@
   </si>
   <si>
     <t>o̤</t>
-  </si>
-  <si>
-    <r>
-      <t>多可高保</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>馬茶下塔押插</t>
-    </r>
   </si>
   <si>
     <t>[*ɒ]</t>
@@ -263,9 +232,6 @@
     </r>
   </si>
   <si>
-    <t>膽籃敢柑三</t>
-  </si>
-  <si>
     <t>[*ɒ̃]</t>
   </si>
   <si>
@@ -314,20 +280,6 @@
     <t>eo</t>
   </si>
   <si>
-    <r>
-      <t>此死</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>過貨保刀桌卓索郭</t>
-    </r>
-  </si>
-  <si>
     <t>[*o]</t>
   </si>
   <si>
@@ -340,20 +292,6 @@
     <t>i</t>
   </si>
   <si>
-    <r>
-      <t>米剃來離</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>字四鐵舌鱉折</t>
-    </r>
-  </si>
-  <si>
     <t>[*i]</t>
   </si>
   <si>
@@ -363,20 +301,6 @@
     <t>u</t>
   </si>
   <si>
-    <r>
-      <t>府務扶付無富</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>牛久丘舊</t>
-    </r>
-  </si>
-  <si>
     <t>[*u]</t>
   </si>
   <si>
@@ -399,20 +323,6 @@
   </si>
   <si>
     <t>ia</t>
-  </si>
-  <si>
-    <r>
-      <t>且社者車借</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>射益赤迹隻</t>
-    </r>
   </si>
   <si>
     <t>[*ia]</t>
@@ -440,9 +350,6 @@
     </r>
   </si>
   <si>
-    <t>丙名領正鏡</t>
-  </si>
-  <si>
     <t>[*ĩã]</t>
   </si>
   <si>
@@ -517,20 +424,6 @@
   </si>
   <si>
     <t>[iəu]</t>
-  </si>
-  <si>
-    <r>
-      <t>標表廟條構厚母</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>惜尺螫</t>
-    </r>
   </si>
   <si>
     <r>
@@ -546,9 +439,6 @@
     </r>
   </si>
   <si>
-    <t>張涼章唱上</t>
-  </si>
-  <si>
     <r>
       <t>[i</t>
     </r>
@@ -642,20 +532,6 @@
   </si>
   <si>
     <t>au</t>
-  </si>
-  <si>
-    <r>
-      <t>包矛炮抄貌</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>偷頭後走九</t>
-    </r>
   </si>
   <si>
     <t>[*au]</t>
@@ -677,26 +553,9 @@
     </r>
   </si>
   <si>
-    <t>□</t>
-  </si>
-  <si>
     <t>o</t>
   </si>
   <si>
-    <r>
-      <t>布圖盧粗輸</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>某畝母牡雺</t>
-    </r>
-  </si>
-  <si>
     <t>[*ou]</t>
   </si>
   <si>
@@ -707,20 +566,6 @@
   </si>
   <si>
     <t>ua</t>
-  </si>
-  <si>
-    <r>
-      <t>瓜花</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>磨我帶蔡話喝割殺</t>
-    </r>
   </si>
   <si>
     <t>[*ua]</t>
@@ -748,9 +593,6 @@
     </r>
   </si>
   <si>
-    <t>搬半滿爛傘</t>
-  </si>
-  <si>
     <t>[*ũã]</t>
   </si>
   <si>
@@ -803,20 +645,6 @@
   </si>
   <si>
     <t>oi</t>
-  </si>
-  <si>
-    <r>
-      <t>梅罪吹衰</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>火果過髮缺啜</t>
-    </r>
   </si>
   <si>
     <t>[*oi]</t>
@@ -841,9 +669,6 @@
     </r>
   </si>
   <si>
-    <t>飯軟磚關遠本門聞</t>
-  </si>
-  <si>
     <t>[*õĩ]</t>
   </si>
   <si>
@@ -903,20 +728,6 @@
   </si>
   <si>
     <t>io̤</t>
-  </si>
-  <si>
-    <r>
-      <t>靴鵝蛇瓦</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>奇寄騎蟻紙</t>
-    </r>
   </si>
   <si>
     <t>[*yɒ]</t>
@@ -947,9 +758,6 @@
     </r>
   </si>
   <si>
-    <t>燃煎泉線件營影聽定鼎</t>
-  </si>
-  <si>
     <r>
       <t>[ỹɒ</t>
     </r>
@@ -998,9 +806,6 @@
     <t>ng</t>
   </si>
   <si>
-    <t>當長唐湯光</t>
-  </si>
-  <si>
     <t>[*ŋ]</t>
   </si>
   <si>
@@ -1010,85 +815,78 @@
     <t>[ŋ]</t>
   </si>
   <si>
-    <t>央黃行方秧</t>
-  </si>
-  <si>
     <t>ang</t>
   </si>
   <si>
-    <r>
-      <t>南淡辦漢簪</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
+    <t>[*aŋ]</t>
+  </si>
+  <si>
+    <t>[aŋ]</t>
+  </si>
+  <si>
+    <t>io̤ng</t>
+  </si>
+  <si>
+    <t>[*yɒŋ]</t>
+  </si>
+  <si>
+    <t>[yɒŋ]</t>
+  </si>
+  <si>
+    <t>[œŋ]</t>
+  </si>
+  <si>
+    <t>[yœŋ]</t>
+  </si>
+  <si>
+    <t>[uɤŋ]</t>
+  </si>
+  <si>
+    <t>[yøŋ]</t>
+  </si>
+  <si>
+    <t>[yɐŋ]</t>
+  </si>
+  <si>
+    <t>[ieŋ]</t>
+  </si>
+  <si>
+    <t>e̤ng</t>
+  </si>
+  <si>
+    <t>建獻練援損村龍終中傳</t>
+  </si>
+  <si>
+    <t>[*œŋ]</t>
+  </si>
+  <si>
+    <t>uang</t>
+  </si>
+  <si>
+    <t>[*uaŋ]</t>
+  </si>
+  <si>
+    <t>[uaŋ]</t>
+  </si>
+  <si>
+    <r>
+      <t>[o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ŋ</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <rFont val="Microsoft JhengHei UI"/>
         <family val="2"/>
       </rPr>
-      <t>飲放網動公</t>
-    </r>
-  </si>
-  <si>
-    <t>[*aŋ]</t>
-  </si>
-  <si>
-    <t>[aŋ]</t>
-  </si>
-  <si>
-    <t>io̤ng</t>
-  </si>
-  <si>
-    <t>良將章糧場</t>
-  </si>
-  <si>
-    <t>[*yɒŋ]</t>
-  </si>
-  <si>
-    <t>[yɒŋ]</t>
-  </si>
-  <si>
-    <t>[œŋ]</t>
-  </si>
-  <si>
-    <t>[yœŋ]</t>
-  </si>
-  <si>
-    <t>[uɤŋ]</t>
-  </si>
-  <si>
-    <t>[yøŋ]</t>
-  </si>
-  <si>
-    <t>[yɐŋ]</t>
-  </si>
-  <si>
-    <t>[ieŋ]</t>
-  </si>
-  <si>
-    <t>e̤ng</t>
-  </si>
-  <si>
-    <t>建獻練援損村龍終中傳</t>
-  </si>
-  <si>
-    <t>[*œŋ]</t>
-  </si>
-  <si>
-    <t>uang</t>
-  </si>
-  <si>
-    <t>彎暖半算官</t>
-  </si>
-  <si>
-    <t>[*uaŋ]</t>
-  </si>
-  <si>
-    <t>[uaŋ]</t>
-  </si>
-  <si>
-    <r>
-      <t>[o</t>
+      <t>/uo</t>
     </r>
     <r>
       <rPr>
@@ -1104,15 +902,248 @@
         <rFont val="Microsoft JhengHei UI"/>
         <family val="2"/>
       </rPr>
-      <t>/uo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>ŋ</t>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>[uəŋ]</t>
+  </si>
+  <si>
+    <t>[uɐŋ]</t>
+  </si>
+  <si>
+    <t>[uoŋ]</t>
+  </si>
+  <si>
+    <t>[ɯəŋ]</t>
+  </si>
+  <si>
+    <t>eong</t>
+  </si>
+  <si>
+    <t>[*oŋ]</t>
+  </si>
+  <si>
+    <t>[ɵŋ]</t>
+  </si>
+  <si>
+    <t>[oŋ]</t>
+  </si>
+  <si>
+    <t>o̤ng</t>
+  </si>
+  <si>
+    <t>郎房網講雙礦宏農風空</t>
+  </si>
+  <si>
+    <t>[*ɒŋ]</t>
+  </si>
+  <si>
+    <t>[ɒŋ]</t>
+  </si>
+  <si>
+    <t>[ɔŋ]</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>羨變天真信等能停定爭</t>
+  </si>
+  <si>
+    <t>[*ɛŋ]</t>
+  </si>
+  <si>
+    <t>[ɛŋ]</t>
+  </si>
+  <si>
+    <t>[ᴇŋ]</t>
+  </si>
+  <si>
+    <t>iang</t>
+  </si>
+  <si>
+    <t>黏尖檢點剪墊碾森參針</t>
+  </si>
+  <si>
+    <t>[*iaŋ]</t>
+  </si>
+  <si>
+    <t>[iæŋ]</t>
+  </si>
+  <si>
+    <t>[iɛŋ]</t>
+  </si>
+  <si>
+    <t>ing</t>
+  </si>
+  <si>
+    <t>[*iŋ]</t>
+  </si>
+  <si>
+    <t>[iŋ]</t>
+  </si>
+  <si>
+    <t>ṳng</t>
+  </si>
+  <si>
+    <t>斤巾近芹恩傾永榮瓊詠</t>
+  </si>
+  <si>
+    <t>[*yŋ]</t>
+  </si>
+  <si>
+    <t>[yŋ]</t>
+  </si>
+  <si>
+    <t>[*aʔ]</t>
+  </si>
+  <si>
+    <t>[aʔ]</t>
+  </si>
+  <si>
+    <t>[*aːʔ]</t>
+  </si>
+  <si>
+    <t>aih</t>
+  </si>
+  <si>
+    <t>[*aiːʔ]</t>
+  </si>
+  <si>
+    <t>a̤h</t>
+  </si>
+  <si>
+    <t>[*eːʔ]</t>
+  </si>
+  <si>
+    <t>a̤uh</t>
+  </si>
+  <si>
+    <t>[*euːʔ]</t>
+  </si>
+  <si>
+    <t>eh</t>
+  </si>
+  <si>
+    <t>[*ɛʔ]</t>
+  </si>
+  <si>
+    <t>[ɛʔ]</t>
+  </si>
+  <si>
+    <t>[ᴇʔ]</t>
+  </si>
+  <si>
+    <t>e̤h</t>
+  </si>
+  <si>
+    <t>閱越決絕月足竹局曲旭</t>
+  </si>
+  <si>
+    <t>[*œʔ]</t>
+  </si>
+  <si>
+    <t>[œʔ]</t>
+  </si>
+  <si>
+    <t>[uɤʔ]</t>
+  </si>
+  <si>
+    <t>[yøʔ]</t>
+  </si>
+  <si>
+    <t>[ieʔ]</t>
+  </si>
+  <si>
+    <t>io̤h</t>
+  </si>
+  <si>
+    <t>[*yɒʔ]</t>
+  </si>
+  <si>
+    <t>[yɒʔ]</t>
+  </si>
+  <si>
+    <t>[yɐʔ]</t>
+  </si>
+  <si>
+    <t>[yœʔ]</t>
+  </si>
+  <si>
+    <t>[*yɒːʔ]</t>
+  </si>
+  <si>
+    <t>uah</t>
+  </si>
+  <si>
+    <t>奪發罰刷伐活</t>
+  </si>
+  <si>
+    <t>[*uaʔ]</t>
+  </si>
+  <si>
+    <t>[uaʔ]</t>
+  </si>
+  <si>
+    <t>[uoʔ]</t>
+  </si>
+  <si>
+    <t>[uəʔ]</t>
+  </si>
+  <si>
+    <t>[uɐʔ]</t>
+  </si>
+  <si>
+    <t>[ɯəʔ]</t>
+  </si>
+  <si>
+    <t>[*uaːʔ]</t>
+  </si>
+  <si>
+    <t>eoh</t>
+  </si>
+  <si>
+    <t>骨術滑出物核</t>
+  </si>
+  <si>
+    <t>[*oʔ]</t>
+  </si>
+  <si>
+    <t>[ɵʔ]</t>
+  </si>
+  <si>
+    <t>[oʔ]</t>
+  </si>
+  <si>
+    <t>[ɒʔ]</t>
+  </si>
+  <si>
+    <t>[*oːʔ]</t>
+  </si>
+  <si>
+    <t>o̤h</t>
+  </si>
+  <si>
+    <t>托鶴各駁樸剝谷服毒木</t>
+  </si>
+  <si>
+    <t>[*ɒʔ]</t>
+  </si>
+  <si>
+    <t>[ɔʔ]</t>
+  </si>
+  <si>
+    <r>
+      <t>[*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ɒːʔ</t>
     </r>
     <r>
       <rPr>
@@ -1124,323 +1155,6 @@
     </r>
   </si>
   <si>
-    <t>[uəŋ]</t>
-  </si>
-  <si>
-    <t>[uɐŋ]</t>
-  </si>
-  <si>
-    <t>[uoŋ]</t>
-  </si>
-  <si>
-    <t>[ɯəŋ]</t>
-  </si>
-  <si>
-    <t>eong</t>
-  </si>
-  <si>
-    <t>分文吞孫君</t>
-  </si>
-  <si>
-    <t>[*oŋ]</t>
-  </si>
-  <si>
-    <t>[ɵŋ]</t>
-  </si>
-  <si>
-    <t>[oŋ]</t>
-  </si>
-  <si>
-    <t>o̤ng</t>
-  </si>
-  <si>
-    <t>郎房網講雙礦宏農風空</t>
-  </si>
-  <si>
-    <t>[*ɒŋ]</t>
-  </si>
-  <si>
-    <t>[ɒŋ]</t>
-  </si>
-  <si>
-    <t>[ɔŋ]</t>
-  </si>
-  <si>
-    <t>eng</t>
-  </si>
-  <si>
-    <t>羨變天真信等能停定爭</t>
-  </si>
-  <si>
-    <t>[*ɛŋ]</t>
-  </si>
-  <si>
-    <t>[ɛŋ]</t>
-  </si>
-  <si>
-    <t>[ᴇŋ]</t>
-  </si>
-  <si>
-    <t>iang</t>
-  </si>
-  <si>
-    <t>黏尖檢點剪墊碾森參針</t>
-  </si>
-  <si>
-    <t>[*iaŋ]</t>
-  </si>
-  <si>
-    <t>[iæŋ]</t>
-  </si>
-  <si>
-    <t>[iɛŋ]</t>
-  </si>
-  <si>
-    <t>ing</t>
-  </si>
-  <si>
-    <r>
-      <t>身民品冰升兵</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>年錢染添</t>
-    </r>
-  </si>
-  <si>
-    <t>[*iŋ]</t>
-  </si>
-  <si>
-    <t>[iŋ]</t>
-  </si>
-  <si>
-    <t>ṳng</t>
-  </si>
-  <si>
-    <t>斤巾近芹恩傾永榮瓊詠</t>
-  </si>
-  <si>
-    <t>[*yŋ]</t>
-  </si>
-  <si>
-    <t>[yŋ]</t>
-  </si>
-  <si>
-    <r>
-      <t>答納八殺確覺</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>目六讀逐</t>
-    </r>
-  </si>
-  <si>
-    <t>[*aʔ]</t>
-  </si>
-  <si>
-    <t>[aʔ]</t>
-  </si>
-  <si>
-    <t>麥白</t>
-  </si>
-  <si>
-    <t>[*aːʔ]</t>
-  </si>
-  <si>
-    <t>aih</t>
-  </si>
-  <si>
-    <t>[*aiːʔ]</t>
-  </si>
-  <si>
-    <t>a̤h</t>
-  </si>
-  <si>
-    <r>
-      <t>疊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>搣摕</t>
-    </r>
-  </si>
-  <si>
-    <t>[*eːʔ]</t>
-  </si>
-  <si>
-    <t>a̤uh</t>
-  </si>
-  <si>
-    <t>着箬石蓆</t>
-  </si>
-  <si>
-    <t>[*euːʔ]</t>
-  </si>
-  <si>
-    <t>eh</t>
-  </si>
-  <si>
-    <t>熱設切實密得色賊格歷</t>
-  </si>
-  <si>
-    <t>[*ɛʔ]</t>
-  </si>
-  <si>
-    <t>[ɛʔ]</t>
-  </si>
-  <si>
-    <t>[ᴇʔ]</t>
-  </si>
-  <si>
-    <t>e̤h</t>
-  </si>
-  <si>
-    <t>閱越決絕月足竹局曲旭</t>
-  </si>
-  <si>
-    <t>[*œʔ]</t>
-  </si>
-  <si>
-    <t>[œʔ]</t>
-  </si>
-  <si>
-    <t>[uɤʔ]</t>
-  </si>
-  <si>
-    <t>[yøʔ]</t>
-  </si>
-  <si>
-    <t>[ieʔ]</t>
-  </si>
-  <si>
-    <t>io̤h</t>
-  </si>
-  <si>
-    <t>雀略躍約着弱</t>
-  </si>
-  <si>
-    <t>[*yɒʔ]</t>
-  </si>
-  <si>
-    <t>[yɒʔ]</t>
-  </si>
-  <si>
-    <t>[yɐʔ]</t>
-  </si>
-  <si>
-    <t>[yœʔ]</t>
-  </si>
-  <si>
-    <t>攑斜越屐揭</t>
-  </si>
-  <si>
-    <t>[*yɒːʔ]</t>
-  </si>
-  <si>
-    <t>uah</t>
-  </si>
-  <si>
-    <t>奪發罰刷伐活</t>
-  </si>
-  <si>
-    <t>[*uaʔ]</t>
-  </si>
-  <si>
-    <t>[uaʔ]</t>
-  </si>
-  <si>
-    <t>[uoʔ]</t>
-  </si>
-  <si>
-    <t>[uəʔ]</t>
-  </si>
-  <si>
-    <t>[uɐʔ]</t>
-  </si>
-  <si>
-    <t>[ɯəʔ]</t>
-  </si>
-  <si>
-    <t>辣活跋蚻捋</t>
-  </si>
-  <si>
-    <t>[*uaːʔ]</t>
-  </si>
-  <si>
-    <t>eoh</t>
-  </si>
-  <si>
-    <t>骨術滑出物核</t>
-  </si>
-  <si>
-    <t>[*oʔ]</t>
-  </si>
-  <si>
-    <t>[ɵʔ]</t>
-  </si>
-  <si>
-    <t>[oʔ]</t>
-  </si>
-  <si>
-    <t>[ɒʔ]</t>
-  </si>
-  <si>
-    <t>鐲學薄落昨</t>
-  </si>
-  <si>
-    <t>[*oːʔ]</t>
-  </si>
-  <si>
-    <t>o̤h</t>
-  </si>
-  <si>
-    <t>托鶴各駁樸剝谷服毒木</t>
-  </si>
-  <si>
-    <t>[*ɒʔ]</t>
-  </si>
-  <si>
-    <t>[ɔʔ]</t>
-  </si>
-  <si>
-    <t>蠟磕踏沓</t>
-  </si>
-  <si>
-    <r>
-      <t>[*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ɒːʔ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
-  </si>
-  <si>
     <t>ih</t>
   </si>
   <si>
@@ -1456,9 +1170,6 @@
     <t>[eʔ]</t>
   </si>
   <si>
-    <t>舌折蝕</t>
-  </si>
-  <si>
     <t>[*iːʔ]</t>
   </si>
   <si>
@@ -1480,25 +1191,16 @@
     <t>[iaʔ]</t>
   </si>
   <si>
-    <t>糴搦食</t>
-  </si>
-  <si>
     <t>[*iaːʔ]</t>
   </si>
   <si>
     <t>oih</t>
   </si>
   <si>
-    <t>襪月物</t>
-  </si>
-  <si>
     <t>[*oiːʔ]</t>
   </si>
   <si>
     <t>uh</t>
-  </si>
-  <si>
-    <t>就複</t>
   </si>
   <si>
     <t>[*uʔ]</t>
@@ -1608,50 +1310,12 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>擺台邁皆解</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>眉師使利滓</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>平病諍星晴</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>閉低犁買麗籬地</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>夾貼帖</t>
-    </r>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>間閒先肩前</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>[ieu]</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>丟籌周守柳</t>
+      <t>加差罷馬佳涯崖_</t>
     </r>
     <r>
       <rPr>
@@ -1659,18 +1323,257 @@
         <sz val="12"/>
         <rFont val="Microsoft JhengHei UI"/>
         <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>百冊隔_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_平病諍星晴_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>閉低犁買麗籬地_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>夾貼帖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_間閒先肩前_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_其咧_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>所初助_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>螺腡坐戴推改脆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_斷卵鑽酸全頓褪_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>多可高保_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>馬茶下塔押插_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_膽籃敢柑三_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>此死_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>過貨保刀桌卓索郭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>米剃來離_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>字四鐵舌鱉折_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>府務扶付無富_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>牛久丘舊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>且社者車借</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>射_益赤迹隻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_丙名領正鏡_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>標表廟條構厚母_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>惜尺螫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_張涼章唱上_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>丟籌周守柳_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
       </rPr>
       <t>柱樹鬚珠</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>其</t>
+    <r>
+      <t>擺台邁皆解_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>眉師使利滓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>加差罷馬佳涯崖</t>
+      <t>包矛炮抄貌_</t>
     </r>
     <r>
       <rPr>
@@ -1678,10 +1581,262 @@
         <sz val="12"/>
         <rFont val="Microsoft JhengHei UI"/>
         <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>百冊隔</t>
-    </r>
+      </rPr>
+      <t>偷頭後走九_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_□_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>布圖盧粗輸_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>某畝母牡雺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>瓜花_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>磨我帶蔡話喝割殺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_搬半滿爛傘_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>梅罪吹衰_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>火果過髮缺啜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_飯軟磚關遠本門聞_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>答納八殺確覺_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>目六讀逐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>身民品冰升兵_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>年錢染添</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>南淡辦漢簪_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>飲放網動公</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_當長唐湯光_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_燃煎泉線件營影聽定鼎_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>靴鵝蛇瓦_</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>奇寄騎蟻紙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_麥白_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_疊搣摕_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_着箬石蓆_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_攑斜越屐揭_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_鐲學薄落昨_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_蠟磕踏沓_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_舌折蝕_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_糴搦食_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_果襪月物_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_即複_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_辣活跋蚻捋_</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>彎暖半算官端團館灌反</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>分文吞孫君尊軍裙粉訓</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>熱設切實密得色賊格歷</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>良將章昌糧場獎揚讓長</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ai]</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雀略躍約着弱虐芍藥腳</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>_央黃行方秧_</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2422,7 +2577,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2447,10 +2602,19 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2465,20 +2629,14 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2859,7 +3017,7 @@
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="1"/>
-    <col min="2" max="2" width="25.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.90625" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" style="1"/>
     <col min="5" max="5" width="10.26953125" style="1" customWidth="1"/>
@@ -2871,35 +3029,35 @@
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" s="14" t="s">
+      <c r="B1" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="18"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="12"/>
     </row>
     <row r="2" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
@@ -2954,18 +3112,18 @@
         <v>19</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="13" t="s">
         <v>21</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -3010,17 +3168,17 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
       <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
@@ -3066,18 +3224,18 @@
         <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="13" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="13" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -3125,16 +3283,16 @@
         <v>27</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="14"/>
       <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="14"/>
       <c r="G6" s="2" t="s">
         <v>30</v>
       </c>
@@ -3180,7 +3338,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>33</v>
@@ -3239,49 +3397,49 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>38</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>26</v>
@@ -3290,53 +3448,53 @@
         <v>26</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="14"/>
+      <c r="G9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>30</v>
@@ -3345,794 +3503,794 @@
         <v>30</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="O10" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="O11" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>56</v>
+        <v>275</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>276</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>65</v>
+        <v>277</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>76</v>
+        <v>67</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+        <v>72</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
       <c r="G17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>88</v>
+        <v>264</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="O18" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="P18" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q18" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="S18" s="10" t="s">
-        <v>86</v>
+        <v>78</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="S18" s="13" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A19" s="7"/>
       <c r="B19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11"/>
+        <v>280</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
+        <v>77</v>
+      </c>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>91</v>
+        <v>281</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
+        <v>261</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
       <c r="G20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A23" s="4" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>105</v>
+        <v>285</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>34</v>
@@ -4185,1207 +4343,1207 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>107</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>114</v>
+        <v>98</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A27" s="4" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>118</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+        <v>103</v>
+      </c>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A28" s="4" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>125</v>
+        <v>108</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="L28" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="O28" s="10" t="s">
-        <v>125</v>
+        <v>110</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="O28" s="13" t="s">
+        <v>109</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q28" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="R28" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="S28" s="10" t="s">
-        <v>125</v>
+        <v>113</v>
+      </c>
+      <c r="Q28" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="R28" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="S28" s="13" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>131</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
+        <v>115</v>
+      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
       <c r="G29" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
+        <v>116</v>
+      </c>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
       <c r="P29" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="11"/>
-      <c r="S29" s="11"/>
+        <v>116</v>
+      </c>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A30" s="4" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>136</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+        <v>119</v>
+      </c>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
       <c r="G30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A31" s="4" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A32" s="4" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>114</v>
+        <v>296</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A33" s="4" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
+        <v>295</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
       <c r="G33" s="2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>159</v>
+        <v>294</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>161</v>
+        <v>139</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="O34" s="10" t="s">
-        <v>161</v>
+        <v>139</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="L34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="N34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="O34" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q34" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="R34" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="S34" s="10" t="s">
-        <v>161</v>
+        <v>139</v>
+      </c>
+      <c r="Q34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="R34" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="S34" s="13" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A35" s="7"/>
       <c r="B35" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C35" s="13"/>
+        <v>314</v>
+      </c>
+      <c r="C35" s="16"/>
       <c r="D35" s="2" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
+        <v>140</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="2" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
+        <v>140</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
       <c r="P35" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
+        <v>140</v>
+      </c>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A36" s="4" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A37" s="4" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>168</v>
+        <v>311</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>171</v>
+        <v>146</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>147</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>174</v>
+        <v>146</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="N37" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="O37" s="13" t="s">
+        <v>150</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q37" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="R37" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="S37" s="10" t="s">
-        <v>171</v>
+        <v>151</v>
+      </c>
+      <c r="Q37" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="R37" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="S37" s="13" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A38" s="4" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
+        <v>147</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
       <c r="G38" s="2" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="11"/>
+        <v>147</v>
+      </c>
+      <c r="M38" s="14"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="14"/>
       <c r="P38" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q38" s="11"/>
-      <c r="R38" s="11"/>
-      <c r="S38" s="11"/>
+        <v>147</v>
+      </c>
+      <c r="Q38" s="14"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="14"/>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>181</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>184</v>
+        <v>158</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>159</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="M39" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="N39" s="12"/>
-      <c r="O39" s="10" t="s">
-        <v>187</v>
+        <v>161</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="N39" s="15"/>
+      <c r="O39" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q39" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="R39" s="10" t="s">
-        <v>188</v>
+        <v>158</v>
+      </c>
+      <c r="Q39" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="R39" s="13" t="s">
+        <v>163</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A40" s="4" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>190</v>
+        <v>309</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E40" s="11"/>
+        <v>166</v>
+      </c>
+      <c r="E40" s="14"/>
       <c r="F40" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
+        <v>167</v>
+      </c>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
       <c r="P40" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q40" s="11"/>
-      <c r="R40" s="11"/>
+        <v>167</v>
+      </c>
+      <c r="Q40" s="14"/>
+      <c r="R40" s="14"/>
       <c r="S40" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A42" s="4" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>203</v>
+        <v>176</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>177</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A43" s="4" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F43" s="11"/>
+        <v>182</v>
+      </c>
+      <c r="F43" s="14"/>
       <c r="G43" s="2" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A44" s="4" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>217</v>
+        <v>291</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="7"/>
       <c r="B47" s="5" t="s">
-        <v>220</v>
+        <v>297</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>21</v>
@@ -5438,72 +5596,72 @@
     </row>
     <row r="48" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="4" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>105</v>
+        <v>285</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>99</v>
+        <v>312</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>225</v>
+        <v>195</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>298</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>26</v>
@@ -5556,929 +5714,929 @@
     </row>
     <row r="50" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="4" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>228</v>
+        <v>299</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A51" s="4" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>231</v>
+        <v>310</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A52" s="4" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>238</v>
+        <v>206</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>206</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="M52" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="N52" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>240</v>
+        <v>206</v>
+      </c>
+      <c r="M52" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="N52" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="O52" s="13" t="s">
+        <v>208</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q52" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="R52" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="S52" s="10" t="s">
-        <v>238</v>
+        <v>206</v>
+      </c>
+      <c r="Q52" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="R52" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="S52" s="13" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A53" s="6" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>243</v>
+        <v>313</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
+        <v>212</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
       <c r="G53" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
+        <v>212</v>
+      </c>
+      <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
+      <c r="O53" s="14"/>
       <c r="P53" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q53" s="11"/>
-      <c r="R53" s="11"/>
-      <c r="S53" s="11"/>
+        <v>213</v>
+      </c>
+      <c r="Q53" s="14"/>
+      <c r="R53" s="14"/>
+      <c r="S53" s="14"/>
     </row>
     <row r="54" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="7"/>
       <c r="B54" s="5" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="7"/>
       <c r="B56" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="6" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>264</v>
+        <v>229</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="7"/>
       <c r="B58" s="5" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A59" s="8" t="s">
-        <v>268</v>
+      <c r="A59" s="17" t="s">
+        <v>232</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>265</v>
+        <v>230</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A60" s="9"/>
+      <c r="A60" s="18"/>
       <c r="B60" s="5" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A61" s="6" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="7"/>
       <c r="B62" s="5" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>280</v>
+        <v>242</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A63" s="6" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>283</v>
+        <v>245</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>284</v>
+        <v>246</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>284</v>
+        <v>246</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="7"/>
       <c r="B64" s="5" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>291</v>
+        <v>251</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="17.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>34</v>
@@ -6531,120 +6689,88 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A67" s="4" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:S1"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="Q18:Q19"/>
-    <mergeCell ref="R18:R19"/>
-    <mergeCell ref="S18:S19"/>
-    <mergeCell ref="S28:S29"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="K28:K29"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="M28:M29"/>
-    <mergeCell ref="N28:N29"/>
-    <mergeCell ref="O28:O29"/>
-    <mergeCell ref="Q28:Q29"/>
-    <mergeCell ref="R28:R29"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="D32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="O52:O53"/>
+    <mergeCell ref="Q52:Q53"/>
+    <mergeCell ref="R52:R53"/>
+    <mergeCell ref="S52:S53"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="N52:N53"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="M52:M53"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="S37:S38"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="R39:R40"/>
     <mergeCell ref="O34:O35"/>
     <mergeCell ref="Q34:Q35"/>
     <mergeCell ref="R34:R35"/>
@@ -6661,29 +6787,61 @@
     <mergeCell ref="L34:L35"/>
     <mergeCell ref="M34:M35"/>
     <mergeCell ref="N34:N35"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="E52:E53"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="M52:M53"/>
-    <mergeCell ref="Q52:Q53"/>
-    <mergeCell ref="R52:R53"/>
-    <mergeCell ref="S52:S53"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="N52:N53"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="O52:O53"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="S28:S29"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="M28:M29"/>
+    <mergeCell ref="N28:N29"/>
+    <mergeCell ref="O28:O29"/>
+    <mergeCell ref="Q28:Q29"/>
+    <mergeCell ref="R28:R29"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="R18:R19"/>
+    <mergeCell ref="S18:S19"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:S1"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
